--- a/Es_13.xlsx
+++ b/Es_13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Documents\Repository\GPOI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5022D3-AE3B-4D2D-8283-5103DE1CE6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D6C72B-8989-4602-8697-2130DDFDEC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{DE866ADC-0768-4BEC-B0D0-BDDECE1DE597}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>DATI</t>
   </si>
@@ -59,7 +59,10 @@
     <t>Abbiamo i punti di un grafico, rappresentandolo viene:</t>
   </si>
   <si>
-    <t>Il punto di equilibrio è quello rappresentato in verde sul grafico</t>
+    <t>Il punto di equilibrio è quello rappresentato in verde sul grafico, il prezzo che corrisponde a questo punti è di €50</t>
+  </si>
+  <si>
+    <t>Quindi il prezzo di equilibrio è di €50</t>
   </si>
 </sst>
 </file>
@@ -83,7 +86,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -111,6 +114,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -148,12 +157,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1716,7 +1725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C48615-AA97-4397-81E8-C9DEABAEC41E}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1724,7 +1733,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1740,109 +1749,106 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>100</v>
       </c>
       <c r="B4" s="2">
         <v>25</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>80</v>
       </c>
       <c r="B5" s="2">
         <v>30</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>70</v>
       </c>
       <c r="B6" s="2">
         <v>35</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>60</v>
       </c>
       <c r="B7" s="2">
         <v>40</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>55</v>
       </c>
       <c r="B8" s="2">
         <v>55</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>50</v>
       </c>
       <c r="B9" s="2">
         <v>75</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>45</v>
       </c>
       <c r="B10" s="2">
         <v>100</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>40</v>
       </c>
       <c r="B11" s="2">
         <v>125</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>30</v>
       </c>
       <c r="B12" s="2">
         <v>150</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>90</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1851,10 +1857,16 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
